--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486758_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486758_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.7789</v>
+        <v>6.111</v>
       </c>
       <c r="E2" t="n">
-        <v>3.0868</v>
+        <v>3.6108</v>
       </c>
       <c r="F2" t="n">
-        <v>3.6921</v>
+        <v>2.5002</v>
       </c>
       <c r="G2" t="n">
         <v>2.745</v>
@@ -610,13 +610,13 @@
         <v>3.2823</v>
       </c>
       <c r="S2" t="n">
-        <v>1.3577</v>
+        <v>0.6898</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.2695</v>
+        <v>-0.7455000000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>2.6273</v>
+        <v>1.4353</v>
       </c>
       <c r="V2" t="n">
         <v>2.29</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. VALVERDE SASTRE</t>
+          <t>A. TORRES MUNICIO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.6024</v>
+        <v>5.8078</v>
       </c>
       <c r="E3" t="n">
-        <v>3.1372</v>
+        <v>4.9658</v>
       </c>
       <c r="F3" t="n">
-        <v>2.4652</v>
+        <v>0.842</v>
       </c>
       <c r="G3" t="n">
-        <v>2.2279</v>
+        <v>2.9702</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7585</v>
+        <v>-1.151</v>
       </c>
       <c r="I3" t="n">
-        <v>1.4694</v>
+        <v>4.1213</v>
       </c>
       <c r="J3" t="n">
-        <v>2.0842</v>
+        <v>4.7793</v>
       </c>
       <c r="K3" t="n">
-        <v>1.311</v>
+        <v>-0.8047</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7732</v>
+        <v>5.584</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1437</v>
+        <v>-1.8091</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.5525</v>
+        <v>-0.3464</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6962</v>
+        <v>-1.4627</v>
       </c>
       <c r="P3" t="n">
-        <v>0.3862</v>
+        <v>-0.5792</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9654</v>
+        <v>-3.8616</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3515</v>
+        <v>3.2823</v>
       </c>
       <c r="S3" t="n">
-        <v>3.1111</v>
+        <v>-0.1861</v>
       </c>
       <c r="T3" t="n">
-        <v>2.6748</v>
+        <v>-0.8627</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4362</v>
+        <v>0.6766</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.1228</v>
+        <v>3.6029</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.6565</v>
+        <v>4.9108</v>
       </c>
       <c r="X3" t="n">
-        <v>0.5337</v>
+        <v>-1.3078</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. TORRES MUNICIO</t>
+          <t>J. VALVERDE SASTRE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.5928</v>
+        <v>3.7463</v>
       </c>
       <c r="E4" t="n">
-        <v>3.9247</v>
+        <v>1.3308</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6681</v>
+        <v>2.4155</v>
       </c>
       <c r="G4" t="n">
-        <v>2.9702</v>
+        <v>2.2279</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.151</v>
+        <v>0.7585</v>
       </c>
       <c r="I4" t="n">
-        <v>4.1213</v>
+        <v>1.4694</v>
       </c>
       <c r="J4" t="n">
-        <v>4.7793</v>
+        <v>2.0842</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.8047</v>
+        <v>1.311</v>
       </c>
       <c r="L4" t="n">
-        <v>5.584</v>
+        <v>0.7732</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.8091</v>
+        <v>0.1437</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3464</v>
+        <v>-0.5525</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.4627</v>
+        <v>0.6962</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.5792</v>
+        <v>0.3862</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.8616</v>
+        <v>-0.9654</v>
       </c>
       <c r="R4" t="n">
-        <v>3.2823</v>
+        <v>1.3515</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.4011</v>
+        <v>1.255</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.9038</v>
+        <v>0.8683999999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5028</v>
+        <v>0.3866</v>
       </c>
       <c r="V4" t="n">
-        <v>3.6029</v>
+        <v>-0.1228</v>
       </c>
       <c r="W4" t="n">
-        <v>4.9108</v>
+        <v>-0.6565</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.3078</v>
+        <v>0.5337</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6038</v>
+        <v>0.6342</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1587</v>
+        <v>-0.1035</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7625</v>
+        <v>0.7377</v>
       </c>
       <c r="G5" t="n">
         <v>-0.2071</v>
@@ -844,13 +844,13 @@
         <v>0.7723</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0386</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2207</v>
+        <v>-0.1655</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2594</v>
+        <v>0.2345</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1847</v>
+        <v>-0.1655</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.9282</v>
+        <v>-1.6109</v>
       </c>
       <c r="F6" t="n">
-        <v>1.7434</v>
+        <v>1.4454</v>
       </c>
       <c r="G6" t="n">
         <v>-1.9845</v>
@@ -922,13 +922,13 @@
         <v>2.7031</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3088</v>
+        <v>-0.2896</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.4072</v>
+        <v>-1.09</v>
       </c>
       <c r="U6" t="n">
-        <v>1.0984</v>
+        <v>0.8004</v>
       </c>
       <c r="V6" t="n">
         <v>0.3709</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.3211</v>
+        <v>-0.1984</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.1911</v>
+        <v>-0.5154</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1299</v>
+        <v>0.317</v>
       </c>
       <c r="G7" t="n">
         <v>0.4142</v>
@@ -1000,13 +1000,13 @@
         <v>2.7031</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.7709</v>
+        <v>-0.6482</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.352</v>
+        <v>-0.6763</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4189</v>
+        <v>0.0281</v>
       </c>
       <c r="V7" t="n">
         <v>-0.7366</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.6738</v>
+        <v>-2.3426</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.7672</v>
+        <v>-3.8085</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0934</v>
+        <v>1.4659</v>
       </c>
       <c r="G8" t="n">
         <v>-4.1327</v>
@@ -1078,13 +1078,13 @@
         <v>2.8962</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3307</v>
+        <v>0.6619</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3042</v>
+        <v>-0.3455</v>
       </c>
       <c r="U8" t="n">
-        <v>0.6348</v>
+        <v>1.0073</v>
       </c>
       <c r="V8" t="n">
         <v>0.1628</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. BECERRA ORDOÑEZ</t>
+          <t>D. MARTINEZ DE LA SERNA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.4201</v>
+        <v>-2.8225</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.4282</v>
+        <v>-3.6105</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.992</v>
+        <v>0.788</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.2874</v>
+        <v>0.289</v>
       </c>
       <c r="H9" t="n">
-        <v>1.4895</v>
+        <v>-0.4072</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.7769</v>
+        <v>0.6962</v>
       </c>
       <c r="J9" t="n">
-        <v>1.5966</v>
+        <v>0.1448</v>
       </c>
       <c r="K9" t="n">
-        <v>1.3524</v>
+        <v>0.1448</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2442</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.884</v>
+        <v>0.1442</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1371</v>
+        <v>-0.5521</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.0211</v>
+        <v>0.6962</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.3862</v>
+        <v>-3.0892</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.8962</v>
+        <v>-3.8616</v>
       </c>
       <c r="R9" t="n">
-        <v>2.51</v>
+        <v>0.7723</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6621</v>
+        <v>0.2207</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4142</v>
+        <v>-0.1794</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2479</v>
+        <v>0.4001</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.0845</v>
+        <v>-0.243</v>
       </c>
       <c r="W9" t="n">
         <v>0.2856</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.3701</v>
+        <v>-0.5286</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. MARTINEZ DE LA SERNA</t>
+          <t>J. BECERRA ORDOÑEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.4625</v>
+        <v>-3.4269</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.9277</v>
+        <v>-1.6832</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4652</v>
+        <v>-1.7437</v>
       </c>
       <c r="G10" t="n">
-        <v>0.289</v>
+        <v>-0.2874</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.4072</v>
+        <v>1.4895</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6962</v>
+        <v>-1.7769</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1448</v>
+        <v>1.5966</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1448</v>
+        <v>1.3524</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>0.2442</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1442</v>
+        <v>-1.884</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.5521</v>
+        <v>0.1371</v>
       </c>
       <c r="O10" t="n">
-        <v>0.6962</v>
+        <v>-2.0211</v>
       </c>
       <c r="P10" t="n">
-        <v>-3.0892</v>
+        <v>-0.3862</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.8616</v>
+        <v>-2.8962</v>
       </c>
       <c r="R10" t="n">
-        <v>0.7723</v>
+        <v>2.51</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4193</v>
+        <v>-0.6688</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4966</v>
+        <v>-0.6692</v>
       </c>
       <c r="U10" t="n">
-        <v>0.07729999999999999</v>
+        <v>0.0004</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.243</v>
+        <v>-2.0845</v>
       </c>
       <c r="W10" t="n">
         <v>0.2856</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.5286</v>
+        <v>-2.3701</v>
       </c>
     </row>
     <row r="11">
@@ -1267,22 +1267,22 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>6.515700000000001</v>
+        <v>7.343400000000003</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.252399999999998</v>
+        <v>-1.424600000000002</v>
       </c>
       <c r="F11" t="n">
         <v>8.767999999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>2.034600000000002</v>
+        <v>2.034600000000001</v>
       </c>
       <c r="H11" t="n">
         <v>1.379</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6555999999999996</v>
+        <v>0.6555999999999997</v>
       </c>
       <c r="J11" t="n">
         <v>12.4261</v>
@@ -1291,7 +1291,7 @@
         <v>4.490500000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>7.935600000000001</v>
+        <v>7.935599999999999</v>
       </c>
       <c r="M11" t="n">
         <v>-10.3915</v>
@@ -1300,10 +1300,10 @@
         <v>-3.1117</v>
       </c>
       <c r="O11" t="n">
-        <v>-7.279800000000001</v>
+        <v>-7.2798</v>
       </c>
       <c r="P11" t="n">
-        <v>0.9654999999999996</v>
+        <v>0.9654999999999997</v>
       </c>
       <c r="Q11" t="n">
         <v>-19.308</v>
@@ -1312,19 +1312,19 @@
         <v>20.2731</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2759000000000003</v>
+        <v>1.1037</v>
       </c>
       <c r="T11" t="n">
-        <v>-4.6934</v>
+        <v>-3.8657</v>
       </c>
       <c r="U11" t="n">
-        <v>4.9694</v>
+        <v>4.9693</v>
       </c>
       <c r="V11" t="n">
         <v>3.2397</v>
       </c>
       <c r="W11" t="n">
-        <v>9.322800000000001</v>
+        <v>9.322799999999999</v>
       </c>
       <c r="X11" t="n">
         <v>-6.083</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. GARCIA GARCIA</t>
+          <t>E. GONZALEZ CAMEJO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>2.1461</v>
+        <v>1.4692</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.597</v>
+        <v>2.7676</v>
       </c>
       <c r="F12" t="n">
-        <v>3.7431</v>
+        <v>-1.2984</v>
       </c>
       <c r="G12" t="n">
-        <v>1.1474</v>
+        <v>2.4113</v>
       </c>
       <c r="H12" t="n">
-        <v>1.5589</v>
+        <v>0.3248</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.4115</v>
+        <v>2.0865</v>
       </c>
       <c r="J12" t="n">
-        <v>1.1148</v>
+        <v>5.7926</v>
       </c>
       <c r="K12" t="n">
-        <v>1.5601</v>
+        <v>1.8432</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.4453</v>
+        <v>3.9494</v>
       </c>
       <c r="M12" t="n">
-        <v>0.0326</v>
+        <v>-3.3813</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.0012</v>
+        <v>-1.5184</v>
       </c>
       <c r="O12" t="n">
-        <v>0.0338</v>
+        <v>-1.8629</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.1931</v>
+        <v>-3.6685</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.0892</v>
+        <v>-6.1785</v>
       </c>
       <c r="R12" t="n">
-        <v>2.8962</v>
+        <v>2.51</v>
       </c>
       <c r="S12" t="n">
-        <v>1.1918</v>
+        <v>-0.1724</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1938</v>
+        <v>-0.9729</v>
       </c>
       <c r="U12" t="n">
-        <v>1.3856</v>
+        <v>0.8006</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>2.8987</v>
       </c>
       <c r="W12" t="n">
-        <v>0.5712</v>
+        <v>4.1264</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.5712</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>E. GONZALEZ CAMEJO</t>
+          <t>J. GARCIA GARCIA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8142</v>
+        <v>1.1131</v>
       </c>
       <c r="E13" t="n">
-        <v>2.2505</v>
+        <v>-2.321</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.4363</v>
+        <v>3.4341</v>
       </c>
       <c r="G13" t="n">
-        <v>2.4113</v>
+        <v>1.1474</v>
       </c>
       <c r="H13" t="n">
-        <v>0.3248</v>
+        <v>1.5589</v>
       </c>
       <c r="I13" t="n">
-        <v>2.0865</v>
+        <v>-0.4115</v>
       </c>
       <c r="J13" t="n">
-        <v>5.7926</v>
+        <v>1.1148</v>
       </c>
       <c r="K13" t="n">
-        <v>1.8432</v>
+        <v>1.5601</v>
       </c>
       <c r="L13" t="n">
-        <v>3.9494</v>
+        <v>-0.4453</v>
       </c>
       <c r="M13" t="n">
-        <v>-3.3813</v>
+        <v>0.0326</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.5184</v>
+        <v>-0.0012</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.8629</v>
+        <v>0.0338</v>
       </c>
       <c r="P13" t="n">
-        <v>-3.6685</v>
+        <v>-0.1931</v>
       </c>
       <c r="Q13" t="n">
-        <v>-6.1785</v>
+        <v>-3.0892</v>
       </c>
       <c r="R13" t="n">
-        <v>2.51</v>
+        <v>2.8962</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.8274</v>
+        <v>0.1588</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.49</v>
+        <v>-0.9177</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6627</v>
+        <v>1.0765</v>
       </c>
       <c r="V13" t="n">
-        <v>2.8987</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>4.1264</v>
+        <v>0.5712</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.2277</v>
+        <v>-0.5712</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1699</v>
+        <v>0.5175</v>
       </c>
       <c r="E14" t="n">
         <v>-1.0064</v>
       </c>
       <c r="F14" t="n">
-        <v>1.1763</v>
+        <v>1.5239</v>
       </c>
       <c r="G14" t="n">
         <v>-1.5002</v>
@@ -1546,13 +1546,13 @@
         <v>2.51</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.4304</v>
+        <v>-0.0828</v>
       </c>
       <c r="T14" t="n">
         <v>-0.5246</v>
       </c>
       <c r="U14" t="n">
-        <v>0.09420000000000001</v>
+        <v>0.4419</v>
       </c>
       <c r="V14" t="n">
         <v>0.9421</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.5723</v>
+        <v>0.0579</v>
       </c>
       <c r="E15" t="n">
-        <v>-2.0103</v>
+        <v>-1.4932</v>
       </c>
       <c r="F15" t="n">
-        <v>1.438</v>
+        <v>1.5511</v>
       </c>
       <c r="G15" t="n">
         <v>0.0569</v>
@@ -1624,13 +1624,13 @@
         <v>3.0892</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.7611</v>
+        <v>-0.1309</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.5452</v>
+        <v>-1.0281</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7841</v>
+        <v>0.8972</v>
       </c>
       <c r="V15" t="n">
         <v>-1.7989</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. RODRIGO HERNÁNDEZ</t>
+          <t>J. GARCIA CABRERA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.8967000000000001</v>
+        <v>-0.4414</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.06900000000000001</v>
+        <v>-1.5336</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.8277</v>
+        <v>1.0922</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.6484</v>
+        <v>0.196</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.7863</v>
+        <v>-0.3104</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1379</v>
+        <v>0.5064</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0414</v>
+        <v>1.2528</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0414</v>
+        <v>-0.5852000000000001</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.838</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.6898</v>
+        <v>-1.0567</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.8277</v>
+        <v>0.2749</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1379</v>
+        <v>-1.3316</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>0.3862</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.9308</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.3169</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2483</v>
+        <v>-0.1242</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1104</v>
+        <v>-0.8556</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1379</v>
+        <v>0.7315</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-0.8995</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.8995</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. GARCIA CABRERA</t>
+          <t>J. RODRIGO HERNÁNDEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.4152</v>
+        <v>-0.8967000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.9473</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5322</v>
+        <v>-0.8277</v>
       </c>
       <c r="G17" t="n">
-        <v>0.196</v>
+        <v>-0.6484</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.3104</v>
+        <v>-0.7863</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5064</v>
+        <v>0.1379</v>
       </c>
       <c r="J17" t="n">
-        <v>1.2528</v>
+        <v>0.0414</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.5852000000000001</v>
+        <v>0.0414</v>
       </c>
       <c r="L17" t="n">
-        <v>1.838</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.0567</v>
+        <v>-0.6898</v>
       </c>
       <c r="N17" t="n">
-        <v>0.2749</v>
+        <v>-0.8277</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.3316</v>
+        <v>0.1379</v>
       </c>
       <c r="P17" t="n">
-        <v>0.3862</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.9308</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.3169</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.0979</v>
+        <v>-0.2483</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.2693</v>
+        <v>-0.1104</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1714</v>
+        <v>-0.1379</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.8995</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.8995</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. SANCHEZ PARRA</t>
+          <t>E. RAMOS BELASTEGUI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.5908</v>
+        <v>-1.5029</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.3168</v>
+        <v>-1.971</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.274</v>
+        <v>0.4681</v>
       </c>
       <c r="G18" t="n">
-        <v>-3.3683</v>
+        <v>-0.8464</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.186</v>
+        <v>-1.3935</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.1824</v>
+        <v>0.5471</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.4365</v>
+        <v>0.3821</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.5993000000000001</v>
+        <v>-0.1515</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1628</v>
+        <v>0.5336</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.9318</v>
+        <v>-1.2285</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.5867</v>
+        <v>-1.242</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.3451</v>
+        <v>0.0135</v>
       </c>
       <c r="P18" t="n">
-        <v>1.1585</v>
+        <v>0.3862</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.1931</v>
+        <v>-1.1585</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3515</v>
+        <v>1.5446</v>
       </c>
       <c r="S18" t="n">
-        <v>0.9046</v>
+        <v>-0.3862</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0272</v>
+        <v>-0.5382</v>
       </c>
       <c r="U18" t="n">
-        <v>0.8774999999999999</v>
+        <v>0.1519</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.2856</v>
+        <v>-0.6565</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2856</v>
+        <v>-0.6565</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.5712</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E. RAMOS BELASTEGUI</t>
+          <t>S. SANCHEZ PARRA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.9829</v>
+        <v>-1.9922</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.1779</v>
+        <v>-0.4202</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1949</v>
+        <v>-1.572</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.8464</v>
+        <v>-3.3683</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.3935</v>
+        <v>-2.186</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5471</v>
+        <v>-1.1824</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3821</v>
+        <v>-0.4365</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.1515</v>
+        <v>-0.5993000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>0.5336</v>
+        <v>0.1628</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.2285</v>
+        <v>-2.9318</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.242</v>
+        <v>-1.5867</v>
       </c>
       <c r="O19" t="n">
-        <v>0.0135</v>
+        <v>-1.3451</v>
       </c>
       <c r="P19" t="n">
-        <v>0.3862</v>
+        <v>1.1585</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1585</v>
+        <v>-0.1931</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5446</v>
+        <v>1.3515</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8662</v>
+        <v>0.5032</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.745</v>
+        <v>-0.0762</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1212</v>
+        <v>0.5795</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.6565</v>
+        <v>-0.2856</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.6565</v>
+        <v>0.2856</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.5712</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.1879</v>
+        <v>-4.1505</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.8938</v>
+        <v>-2.7212</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.2941</v>
+        <v>-1.4293</v>
       </c>
       <c r="G20" t="n">
         <v>0.5171</v>
@@ -2014,13 +2014,13 @@
         <v>3.0892</v>
       </c>
       <c r="S20" t="n">
-        <v>1.8589</v>
+        <v>0.8963</v>
       </c>
       <c r="T20" t="n">
-        <v>0.8818</v>
+        <v>0.0545</v>
       </c>
       <c r="U20" t="n">
-        <v>0.9771</v>
+        <v>0.8418</v>
       </c>
       <c r="V20" t="n">
         <v>-3.4401</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-6.5156</v>
+        <v>-5.826</v>
       </c>
       <c r="E21" t="n">
         <v>-8.768000000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>2.2524</v>
+        <v>2.942</v>
       </c>
       <c r="G21" t="n">
         <v>-2.0346</v>
@@ -2092,13 +2092,13 @@
         <v>19.3076</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.276</v>
+        <v>0.4135</v>
       </c>
       <c r="T21" t="n">
-        <v>-4.9693</v>
+        <v>-4.9692</v>
       </c>
       <c r="U21" t="n">
-        <v>4.693499999999999</v>
+        <v>5.383</v>
       </c>
       <c r="V21" t="n">
         <v>-3.2398</v>
